--- a/soilgrids_vs_field_statistics.xlsx
+++ b/soilgrids_vs_field_statistics.xlsx
@@ -1,126 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Soilgrids\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5A76296-2682-47CD-A7FF-91BA9172DCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView minimized="1" xWindow="5355" yWindow="5340" windowWidth="18000" windowHeight="9270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Statistics" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statistics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
-  <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>Bias (SG−Field)</t>
-  </si>
-  <si>
-    <t>MAE</t>
-  </si>
-  <si>
-    <t>RMSE</t>
-  </si>
-  <si>
-    <t>rRMSE (%)</t>
-  </si>
-  <si>
-    <t>Wilcoxon W</t>
-  </si>
-  <si>
-    <t>p-value (Wilcoxon)</t>
-  </si>
-  <si>
-    <t>Significance</t>
-  </si>
-  <si>
-    <t>Bulk density</t>
-  </si>
-  <si>
-    <t>g/cm³</t>
-  </si>
-  <si>
-    <t>Field capacity</t>
-  </si>
-  <si>
-    <t>cm³/cm³</t>
-  </si>
-  <si>
-    <t>Wilting point</t>
-  </si>
-  <si>
-    <t>Near-saturation (10 kPa)</t>
-  </si>
-  <si>
-    <t>p&lt;0.001</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E88E5"/>
-        <bgColor rgb="FF1E88E5"/>
+        <fgColor rgb="001E88E5"/>
+        <bgColor rgb="001E88E5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF9C4"/>
-        <bgColor rgb="FFFFF9C4"/>
+        <fgColor rgb="00FFF9C4"/>
+        <bgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -136,35 +62,85 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -452,209 +428,231 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="5" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="22.42578125" customWidth="1"/>
-    <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="4"/>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Bias (SG-Field)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>rRMSE (%)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Wilcoxon W</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>p-value (Wilcoxon)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Significance</t>
+        </is>
+      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="2">
-        <v>38</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0.66491999999999996</v>
-      </c>
-      <c r="H2" s="2">
-        <v>0.66491999999999996</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0.66937000000000002</v>
-      </c>
-      <c r="J2" s="2">
-        <v>173.47</v>
-      </c>
-      <c r="K2" s="4"/>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Bulk density</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>g/cm3</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.69985</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.69985</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.7066</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>198.15</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="2">
-        <v>38</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="2">
-        <v>-0.26146999999999998</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0.26146999999999998</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0.27368999999999999</v>
-      </c>
-      <c r="J3" s="2">
-        <v>44.31</v>
-      </c>
-      <c r="K3" s="4"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Field capacity</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>cm3/cm3</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>-0.27008</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.27008</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.28029</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>45.04</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2">
-        <v>38</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="2">
-        <v>-0.16850999999999999</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0.16850999999999999</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0.17723</v>
-      </c>
-      <c r="J4" s="2">
-        <v>52.72</v>
-      </c>
-      <c r="K4" s="4"/>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Wilting point</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>cm3/cm3</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>-0.15927</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.15927</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.16896</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>51.81</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="2">
-        <v>38</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="2">
-        <v>-0.39028000000000002</v>
-      </c>
-      <c r="H5" s="2">
-        <v>0.39028000000000002</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0.39150000000000001</v>
-      </c>
-      <c r="J5" s="2">
-        <v>48.34</v>
-      </c>
-      <c r="K5" s="4"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="5"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K7" s="4"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K8" s="4"/>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Near-saturation (10 kPa)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>cm3/cm3</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>-0.40875</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.40875</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>49.93</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/soilgrids_vs_field_statistics.xlsx
+++ b/soilgrids_vs_field_statistics.xlsx
@@ -588,19 +588,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-0.15927</v>
+        <v>-0.15944</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.15927</v>
+        <v>0.15944</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.16896</v>
+        <v>0.16931</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>51.81</v>
+        <v>51.91</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>0</v>
